--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-specimen-pathology.xlsx
@@ -434,7 +434,7 @@
     <t>Specimen.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -472,7 +472,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -761,7 +761,7 @@
     <t>Specimen.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -780,7 +780,7 @@
     <t>Specimen.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -884,7 +884,7 @@
     <t>Specimen.collection.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1027,7 +1027,7 @@
     <t>Specimen.processing.additive</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Substance)
+    <t xml:space="preserve">Reference(Substance|4.0.1)
 </t>
   </si>
   <si>
@@ -1131,7 +1131,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance)</t>
+Reference(Substance|4.0.1)</t>
   </si>
   <si>
     <t>容器内の添加物。【詳細参照】</t>
